--- a/Configuración_memoria.xlsx
+++ b/Configuración_memoria.xlsx
@@ -8,13 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joleh\Desktop\MII\SEGUNDO\2Cuatrimestre\IIA\RPA_Jolehisy_Acevedo_Medina\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07649F5D-9419-4D1B-B406-C4A96EBAE43B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA717852-D907-46F5-839D-B9F0DDBFD024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{60E53714-B544-4A41-8E06-72AD90D772D2}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="30960" windowHeight="16800" firstSheet="1" activeTab="7" xr2:uid="{60E53714-B544-4A41-8E06-72AD90D772D2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
+    <sheet name="PORTADA" sheetId="4" r:id="rId1"/>
+    <sheet name="MEMORIA ETIQUETAS" sheetId="1" r:id="rId2"/>
+    <sheet name="MEMORIA TABLAS" sheetId="2" r:id="rId3"/>
+    <sheet name="DATOS IMÁGENES" sheetId="9" r:id="rId4"/>
+    <sheet name="MEMORIA CUADROS" sheetId="3" r:id="rId5"/>
+    <sheet name="ANEXO DISP MIN" sheetId="5" r:id="rId6"/>
+    <sheet name="EBSS" sheetId="6" r:id="rId7"/>
+    <sheet name="PERSONAL_EBSS" sheetId="7" r:id="rId8"/>
+    <sheet name="PLIEGO CONDICIONES" sheetId="8" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="105">
   <si>
     <t>Etiqueta</t>
   </si>
@@ -93,9 +100,6 @@
     <t>[[USO_ANTERIOR]]</t>
   </si>
   <si>
-    <t>[[NUEVA_ACTIVIDAD]]</t>
-  </si>
-  <si>
     <t>[[actividad principal]]</t>
   </si>
   <si>
@@ -169,26 +173,208 @@
   </si>
   <si>
     <t>[[CUADRO DE SUPERFICIES]]</t>
+  </si>
+  <si>
+    <t>[[TABLA IMPACTO ELEMENTOS FIJOS]]</t>
+  </si>
+  <si>
+    <t>[NOMBRE EMPRESA]</t>
+  </si>
+  <si>
+    <t>[DIRECCIÓN DEL ESTABLECIMIENTO]</t>
+  </si>
+  <si>
+    <t>[MES]</t>
+  </si>
+  <si>
+    <t>[AÑO]</t>
+  </si>
+  <si>
+    <t>[[NOMBRE EMPRESA]]</t>
+  </si>
+  <si>
+    <t>[[encabezado]]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[días realización obra]] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">[[operarios trabajando]] </t>
+  </si>
+  <si>
+    <t>Personal</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>INSTALADOR BT</t>
+  </si>
+  <si>
+    <t>INSTALADOR PCI</t>
+  </si>
+  <si>
+    <t>INSTALADOR PLADUR</t>
+  </si>
+  <si>
+    <t>INSTALADOR CLIMATIZACIÓN</t>
+  </si>
+  <si>
+    <t>INSTALADOR VENTILACIÓN</t>
+  </si>
+  <si>
+    <t>CERRAJERO</t>
+  </si>
+  <si>
+    <t>PINTOR</t>
+  </si>
+  <si>
+    <t>CARPINTERO</t>
+  </si>
+  <si>
+    <t>ALLBAÑIL</t>
+  </si>
+  <si>
+    <t>ACRISTALADOR</t>
+  </si>
+  <si>
+    <t>Dirección</t>
+  </si>
+  <si>
+    <t>[[ENCABEZADO]]</t>
+  </si>
+  <si>
+    <t>Alisios</t>
+  </si>
+  <si>
+    <t>Calle Alisios, nº23, 38650, Santa Cruz de Tenerife</t>
+  </si>
+  <si>
+    <t>junio</t>
+  </si>
+  <si>
+    <t>una nave</t>
+  </si>
+  <si>
+    <t>de la nave</t>
+  </si>
+  <si>
+    <t>la nave</t>
+  </si>
+  <si>
+    <t>PROYECTO DE ACTIVIDAD E INSTALACIONES PARA ALISIOS S.L.</t>
+  </si>
+  <si>
+    <t>almacenamiento de materiales de construcción y oficinas técnicas y administrativas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle Alisios </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> existentes</t>
+  </si>
+  <si>
+    <t>Granadilla de Abona</t>
+  </si>
+  <si>
+    <t>Alisios S.L.</t>
+  </si>
+  <si>
+    <t>B7454745</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Tercer</t>
+  </si>
+  <si>
+    <t>Lunes-Viernes</t>
+  </si>
+  <si>
+    <t>primera</t>
+  </si>
+  <si>
+    <t>unisex</t>
+  </si>
+  <si>
+    <t>8:00-16:00</t>
+  </si>
+  <si>
+    <t>Al lado de la puerta principal</t>
+  </si>
+  <si>
+    <t>[[jornadas]]</t>
+  </si>
+  <si>
+    <t>Tipo de uso</t>
+  </si>
+  <si>
+    <t>Ruta</t>
+  </si>
+  <si>
+    <t>Administrativo</t>
+  </si>
+  <si>
+    <t>Aparcamiento</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Docente</t>
+  </si>
+  <si>
+    <t>Hospitalario</t>
+  </si>
+  <si>
+    <t>Pública Concurrencia</t>
+  </si>
+  <si>
+    <t>Residencial Público</t>
+  </si>
+  <si>
+    <t>Residencial Vivienda</t>
+  </si>
+  <si>
+    <t>C:\Users\joleh\Dropbox\INGENIERIA\IMÁGENES DB SI 4\Aparcamiento.png</t>
+  </si>
+  <si>
+    <t>C:\Users\joleh\Dropbox\INGENIERIA\IMÁGENES DB SI 4\Administrativo.png</t>
+  </si>
+  <si>
+    <t>C:\Users\joleh\Dropbox\INGENIERIA\IMÁGENES DB SI 4\Comercial.png</t>
+  </si>
+  <si>
+    <t>C:\Users\joleh\Dropbox\INGENIERIA\IMÁGENES DB SI 4\Docente.png</t>
+  </si>
+  <si>
+    <t>C:\Users\joleh\Dropbox\INGENIERIA\IMÁGENES DB SI 4\Hospitalario.png</t>
+  </si>
+  <si>
+    <t>C:\Users\joleh\Dropbox\INGENIERIA\IMÁGENES DB SI 4\Pública Concurrencia.png</t>
+  </si>
+  <si>
+    <t>C:\Users\joleh\Dropbox\INGENIERIA\IMÁGENES DB SI 4\Residencial Público.png</t>
+  </si>
+  <si>
+    <t>C:\Users\joleh\Dropbox\INGENIERIA\IMÁGENES DB SI 4\Residencial Vivienda.png</t>
+  </si>
+  <si>
+    <t>SI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFEE0000"/>
-      <name val="Swis721 Lt BT"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -200,6 +386,17 @@
       <sz val="10"/>
       <name val="Swis721 Lt BT"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Swis721 Lt BT"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -237,24 +434,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -589,269 +801,53 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65B2C45C-01FA-4FCB-96EF-789294F30345}">
-  <dimension ref="A1:H34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26C40000-82D8-454A-9C9B-540261EBE902}">
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="4"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="H30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+      <c r="B1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="6">
+        <v>2026</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -859,26 +855,797 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65B2C45C-01FA-4FCB-96EF-789294F30345}">
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="77" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="3" t="str">
+        <f>PORTADA!B2</f>
+        <v>Alisios</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="3" t="str">
+        <f>PORTADA!B3</f>
+        <v>Calle Alisios, nº23, 38650, Santa Cruz de Tenerife</v>
+      </c>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="3">
+        <v>101</v>
+      </c>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="3" t="str">
+        <f>PORTADA!B4</f>
+        <v>junio</v>
+      </c>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="3">
+        <f>PORTADA!B5</f>
+        <v>2026</v>
+      </c>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="3">
+        <v>10</v>
+      </c>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="12">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="12">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="3">
+        <v>2</v>
+      </c>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="3">
+        <v>1450</v>
+      </c>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="3">
+        <v>2540</v>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="H29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="3">
+        <v>4</v>
+      </c>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25518112-FAD8-435E-A79E-5678ABDD1B94}">
-  <dimension ref="A2:A4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="7" t="str">
+        <f>IFERROR(_xlfn.XLOOKUP(B2, 'DATOS IMÁGENES'!A:A, 'DATOS IMÁGENES'!B:B), "")</f>
+        <v>C:\Users\joleh\Dropbox\INGENIERIA\IMÁGENES DB SI 4\Administrativo.png</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5E6FE01D-BA46-451D-BC30-8E0D7E8F9E85}">
+          <x14:formula1>
+            <xm:f>'DATOS IMÁGENES'!$A$2:$A$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{295CB875-ECEF-4153-A6DF-F6C3CA5C17F4}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A587E1C2-C186-4C0C-9F04-A5C8C9B446D2}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="7"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B3" s="7"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
         <v>42</v>
+      </c>
+      <c r="B4" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34EA27BE-B90F-4CCE-9104-097EDFCE9700}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <f>PORTADA!B2</f>
+        <v>Alisios</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <f>'MEMORIA ETIQUETAS'!B4</f>
+        <v>la nave</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <f>PORTADA!B4</f>
+        <v>junio</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2">
+        <f>PORTADA!B5</f>
+        <v>2026</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{365D257F-BA04-4F3E-9E12-7A2A975A2654}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="77" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="6" t="str">
+        <f>'MEMORIA ETIQUETAS'!B2</f>
+        <v>una nave</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <f>'MEMORIA ETIQUETAS'!B5</f>
+        <v>PROYECTO DE ACTIVIDAD E INSTALACIONES PARA ALISIOS S.L.</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="6" t="str">
+        <f>'MEMORIA ETIQUETAS'!B6</f>
+        <v>almacenamiento de materiales de construcción y oficinas técnicas y administrativas</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="6">
+        <f>B5*B6</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <f>PORTADA!B4</f>
+        <v>junio</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="6">
+        <f>PORTADA!B5</f>
+        <v>2026</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C336D582-9648-4283-A635-299E04FA3683}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="7"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="7"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="7"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C6A815-6FC3-46C7-A214-07DE3B934E4C}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="6" t="str">
+        <f>'MEMORIA ETIQUETAS'!B5</f>
+        <v>PROYECTO DE ACTIVIDAD E INSTALACIONES PARA ALISIOS S.L.</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <f>PORTADA!B4</f>
+        <v>junio</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="6">
+        <f>PORTADA!B5</f>
+        <v>2026</v>
       </c>
     </row>
   </sheetData>
